--- a/data/25-26Fall.xlsx
+++ b/data/25-26Fall.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SchedulingTHeoryFinalExamSchedulingBerk\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e402f802124af4b/Masaüstü/Projects/Campus-Scheduling/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="13" documentId="11_2A3D1E90BCA267A2EE52F243E8B62DAD2EF156C3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9ED17C8-6EF5-4DCD-A716-F60C1262F829}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12780" windowHeight="3915"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -1637,7 +1638,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1685,6 +1686,44 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AFEECD5C-1C09-4C4B-8C93-B8EB0BA1154E}" name="Table1" displayName="Table1" ref="A1:T534" totalsRowShown="0">
+  <autoFilter ref="A1:T534" xr:uid="{AFEECD5C-1C09-4C4B-8C93-B8EB0BA1154E}">
+    <filterColumn colId="12">
+      <filters>
+        <filter val="3"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A40:T533">
+    <sortCondition ref="E1:E534"/>
+  </sortState>
+  <tableColumns count="20">
+    <tableColumn id="1" xr3:uid="{71FCC2CF-D0F8-4FBF-825C-B05AC7152D00}" name="FacultyName"/>
+    <tableColumn id="2" xr3:uid="{91ACE320-102E-45FF-A055-B48C25E9FD7F}" name="FacultyCode"/>
+    <tableColumn id="3" xr3:uid="{AFABC9EF-7D17-4627-80DE-38CFAA3441FB}" name="DepartmentCode"/>
+    <tableColumn id="4" xr3:uid="{3B9F2555-7833-479B-AAC0-2EF82E2FC1E5}" name="DepartmentName"/>
+    <tableColumn id="5" xr3:uid="{2273ACC3-2DC1-4FC3-A799-57FA551DB099}" name="CourseCode"/>
+    <tableColumn id="6" xr3:uid="{25AF47E5-DD9F-4536-A35F-AB32851FFC5A}" name="CourseName"/>
+    <tableColumn id="7" xr3:uid="{AC914EB0-347B-417B-BC01-4AB894122C33}" name="CourseId"/>
+    <tableColumn id="8" xr3:uid="{769FF7B1-C1FC-497D-9F50-4B4E0D4F54C3}" name="EducationType"/>
+    <tableColumn id="9" xr3:uid="{DFF61974-C5AF-4D19-8CBF-B6E5BFE94B6D}" name="CourseSectionCode"/>
+    <tableColumn id="10" xr3:uid="{CC55DA3A-CB66-466C-8D7D-BD67106C7FFD}" name="AKTS"/>
+    <tableColumn id="11" xr3:uid="{955C4655-EE31-48CC-BACA-887628B58EA9}" name="DERS_ID"/>
+    <tableColumn id="12" xr3:uid="{2B7CC818-1CFE-4157-AB13-142BD615706B}" name="DONEM_TIP"/>
+    <tableColumn id="13" xr3:uid="{62C5C083-6C25-4105-BCEA-3F4B343193AB}" name="KREDI"/>
+    <tableColumn id="14" xr3:uid="{9EEBF3C9-2B70-4010-BC38-E1752E9F27CB}" name="LAB_SAAT"/>
+    <tableColumn id="15" xr3:uid="{200229C9-3C84-4A52-A97A-220ACABCCCD6}" name="SINIF"/>
+    <tableColumn id="16" xr3:uid="{61FD06AC-ACC8-45B8-8743-A5070E03F74B}" name="TEO_SAAT"/>
+    <tableColumn id="17" xr3:uid="{255630AB-1406-4615-B1D1-EA6465212429}" name="UYG_SAAT"/>
+    <tableColumn id="18" xr3:uid="{34266694-672F-4BA8-913F-0AE3EAF138FD}" name="ZOR_SEC"/>
+    <tableColumn id="19" xr3:uid="{870165AD-3704-42B4-B7B1-85CA577F20DE}" name="InstructorUserId"/>
+    <tableColumn id="20" xr3:uid="{6D08AC03-6B31-4F97-9829-E6169D6B357F}" name="OgrenciSayisi"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1949,14 +1988,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T534"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1328125" customWidth="1"/>
+    <col min="3" max="3" width="16.06640625" customWidth="1"/>
+    <col min="4" max="4" width="16.796875" customWidth="1"/>
+    <col min="5" max="5" width="11.86328125" customWidth="1"/>
+    <col min="6" max="6" width="23.6640625" customWidth="1"/>
+    <col min="7" max="7" width="9.3984375" customWidth="1"/>
+    <col min="8" max="8" width="14.1328125" customWidth="1"/>
+    <col min="9" max="9" width="17.59765625" customWidth="1"/>
+    <col min="11" max="11" width="9.265625" customWidth="1"/>
+    <col min="12" max="12" width="12.265625" customWidth="1"/>
+    <col min="14" max="14" width="10.59765625" customWidth="1"/>
+    <col min="16" max="16" width="10.73046875" customWidth="1"/>
+    <col min="17" max="17" width="11" customWidth="1"/>
+    <col min="18" max="18" width="9.59765625" customWidth="1"/>
+    <col min="19" max="19" width="15.33203125" customWidth="1"/>
+    <col min="20" max="20" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2018,7 +2073,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -2080,7 +2135,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -2142,7 +2197,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -2204,7 +2259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -2266,7 +2321,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -2328,7 +2383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -2390,7 +2445,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -2452,7 +2507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -2514,7 +2569,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>20</v>
       </c>
@@ -2576,7 +2631,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -2638,7 +2693,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -2700,7 +2755,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -2762,7 +2817,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -2824,7 +2879,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -2886,7 +2941,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -2948,7 +3003,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -3010,7 +3065,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -3072,7 +3127,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -3134,7 +3189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -3196,7 +3251,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -3258,7 +3313,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -3320,7 +3375,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>20</v>
       </c>
@@ -3382,7 +3437,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>20</v>
       </c>
@@ -3444,7 +3499,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>20</v>
       </c>
@@ -3506,7 +3561,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>20</v>
       </c>
@@ -3568,7 +3623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>20</v>
       </c>
@@ -3630,7 +3685,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>20</v>
       </c>
@@ -3692,7 +3747,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>20</v>
       </c>
@@ -3754,7 +3809,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>20</v>
       </c>
@@ -3816,7 +3871,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>20</v>
       </c>
@@ -3878,7 +3933,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>20</v>
       </c>
@@ -3940,7 +3995,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>20</v>
       </c>
@@ -4002,7 +4057,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>20</v>
       </c>
@@ -4064,7 +4119,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>20</v>
       </c>
@@ -4126,7 +4181,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>20</v>
       </c>
@@ -4188,7 +4243,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>20</v>
       </c>
@@ -4250,7 +4305,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>20</v>
       </c>
@@ -4312,7 +4367,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>20</v>
       </c>
@@ -4374,7 +4429,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>20</v>
       </c>
@@ -4382,37 +4437,37 @@
         <v>8</v>
       </c>
       <c r="C40">
-        <v>808</v>
+        <v>39</v>
       </c>
       <c r="D40" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E40" t="s">
-        <v>75</v>
+        <v>280</v>
       </c>
       <c r="F40" t="s">
-        <v>76</v>
+        <v>281</v>
       </c>
       <c r="G40">
-        <v>6346757</v>
+        <v>6346708</v>
       </c>
       <c r="H40" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="I40">
         <v>1</v>
       </c>
       <c r="J40">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K40">
-        <v>6346757</v>
+        <v>6346708</v>
       </c>
       <c r="L40" t="s">
         <v>25</v>
       </c>
       <c r="M40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N40">
         <v>0</v>
@@ -4421,7 +4476,7 @@
         <v>4</v>
       </c>
       <c r="P40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -4430,13 +4485,13 @@
         <v>26</v>
       </c>
       <c r="S40">
-        <v>6792717</v>
+        <v>3415337</v>
       </c>
       <c r="T40">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>20</v>
       </c>
@@ -4444,19 +4499,19 @@
         <v>8</v>
       </c>
       <c r="C41">
-        <v>39</v>
+        <v>808</v>
       </c>
       <c r="D41" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E41" t="s">
-        <v>75</v>
+        <v>280</v>
       </c>
       <c r="F41" t="s">
-        <v>76</v>
+        <v>281</v>
       </c>
       <c r="G41">
-        <v>6346719</v>
+        <v>6346708</v>
       </c>
       <c r="H41" t="s">
         <v>24</v>
@@ -4465,16 +4520,16 @@
         <v>1</v>
       </c>
       <c r="J41">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K41">
-        <v>6346719</v>
+        <v>6346708</v>
       </c>
       <c r="L41" t="s">
         <v>25</v>
       </c>
       <c r="M41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N41">
         <v>0</v>
@@ -4483,7 +4538,7 @@
         <v>4</v>
       </c>
       <c r="P41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -4492,13 +4547,13 @@
         <v>26</v>
       </c>
       <c r="S41">
-        <v>1635809</v>
+        <v>3415337</v>
       </c>
       <c r="T41">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>20</v>
       </c>
@@ -4560,7 +4615,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>20</v>
       </c>
@@ -4622,7 +4677,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>20</v>
       </c>
@@ -4684,7 +4739,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>20</v>
       </c>
@@ -4746,7 +4801,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>20</v>
       </c>
@@ -4808,7 +4863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>20</v>
       </c>
@@ -4870,7 +4925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>20</v>
       </c>
@@ -4932,7 +4987,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>20</v>
       </c>
@@ -4994,7 +5049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>20</v>
       </c>
@@ -5056,7 +5111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>20</v>
       </c>
@@ -5118,7 +5173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>20</v>
       </c>
@@ -5180,7 +5235,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>20</v>
       </c>
@@ -5242,7 +5297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>20</v>
       </c>
@@ -5304,7 +5359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>20</v>
       </c>
@@ -5366,7 +5421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>20</v>
       </c>
@@ -5428,7 +5483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>20</v>
       </c>
@@ -5490,7 +5545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>20</v>
       </c>
@@ -5552,7 +5607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>20</v>
       </c>
@@ -5614,7 +5669,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>20</v>
       </c>
@@ -5676,7 +5731,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>20</v>
       </c>
@@ -5690,13 +5745,13 @@
         <v>52</v>
       </c>
       <c r="E61" t="s">
-        <v>95</v>
+        <v>121</v>
       </c>
       <c r="F61" t="s">
-        <v>96</v>
+        <v>122</v>
       </c>
       <c r="G61">
-        <v>6346710</v>
+        <v>6346709</v>
       </c>
       <c r="H61" t="s">
         <v>24</v>
@@ -5708,7 +5763,7 @@
         <v>5</v>
       </c>
       <c r="K61">
-        <v>6346710</v>
+        <v>6346709</v>
       </c>
       <c r="L61" t="s">
         <v>25</v>
@@ -5732,13 +5787,13 @@
         <v>26</v>
       </c>
       <c r="S61">
-        <v>1540100</v>
+        <v>4321939</v>
       </c>
       <c r="T61">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>20</v>
       </c>
@@ -5752,16 +5807,16 @@
         <v>54</v>
       </c>
       <c r="E62" t="s">
-        <v>95</v>
+        <v>121</v>
       </c>
       <c r="F62" t="s">
-        <v>96</v>
+        <v>122</v>
       </c>
       <c r="G62">
-        <v>6346747</v>
+        <v>6346709</v>
       </c>
       <c r="H62" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="I62">
         <v>1</v>
@@ -5770,7 +5825,7 @@
         <v>5</v>
       </c>
       <c r="K62">
-        <v>6346747</v>
+        <v>6346709</v>
       </c>
       <c r="L62" t="s">
         <v>25</v>
@@ -5794,13 +5849,13 @@
         <v>26</v>
       </c>
       <c r="S62">
-        <v>1540100</v>
+        <v>4321939</v>
       </c>
       <c r="T62">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>20</v>
       </c>
@@ -5862,7 +5917,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>20</v>
       </c>
@@ -5870,22 +5925,22 @@
         <v>8</v>
       </c>
       <c r="C64">
-        <v>808</v>
+        <v>39</v>
       </c>
       <c r="D64" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E64" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F64" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G64">
-        <v>6346752</v>
+        <v>6346710</v>
       </c>
       <c r="H64" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="I64">
         <v>1</v>
@@ -5894,7 +5949,7 @@
         <v>5</v>
       </c>
       <c r="K64">
-        <v>6346752</v>
+        <v>6346710</v>
       </c>
       <c r="L64" t="s">
         <v>25</v>
@@ -5918,13 +5973,13 @@
         <v>26</v>
       </c>
       <c r="S64">
-        <v>3218866</v>
+        <v>1540100</v>
       </c>
       <c r="T64">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>20</v>
       </c>
@@ -5932,22 +5987,22 @@
         <v>8</v>
       </c>
       <c r="C65">
-        <v>39</v>
+        <v>808</v>
       </c>
       <c r="D65" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E65" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F65" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G65">
-        <v>6346715</v>
+        <v>6346747</v>
       </c>
       <c r="H65" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="I65">
         <v>1</v>
@@ -5956,7 +6011,7 @@
         <v>5</v>
       </c>
       <c r="K65">
-        <v>6346715</v>
+        <v>6346747</v>
       </c>
       <c r="L65" t="s">
         <v>25</v>
@@ -5980,13 +6035,13 @@
         <v>26</v>
       </c>
       <c r="S65">
-        <v>3218866</v>
+        <v>1540100</v>
       </c>
       <c r="T65">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>20</v>
       </c>
@@ -6048,7 +6103,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>20</v>
       </c>
@@ -6110,7 +6165,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>20</v>
       </c>
@@ -6172,7 +6227,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>20</v>
       </c>
@@ -6234,7 +6289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>20</v>
       </c>
@@ -6296,7 +6351,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
         <v>20</v>
       </c>
@@ -6358,7 +6413,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
         <v>20</v>
       </c>
@@ -6420,7 +6475,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>20</v>
       </c>
@@ -6482,7 +6537,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
         <v>20</v>
       </c>
@@ -6544,7 +6599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>20</v>
       </c>
@@ -6606,7 +6661,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>20</v>
       </c>
@@ -6668,7 +6723,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
         <v>20</v>
       </c>
@@ -6730,7 +6785,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
         <v>20</v>
       </c>
@@ -6792,7 +6847,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>20</v>
       </c>
@@ -6854,7 +6909,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>20</v>
       </c>
@@ -6916,7 +6971,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>20</v>
       </c>
@@ -6978,7 +7033,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>20</v>
       </c>
@@ -7040,7 +7095,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>20</v>
       </c>
@@ -7102,7 +7157,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>20</v>
       </c>
@@ -7164,7 +7219,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>20</v>
       </c>
@@ -7226,7 +7281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>20</v>
       </c>
@@ -7288,7 +7343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>20</v>
       </c>
@@ -7302,13 +7357,13 @@
         <v>52</v>
       </c>
       <c r="E87" t="s">
-        <v>121</v>
+        <v>419</v>
       </c>
       <c r="F87" t="s">
-        <v>122</v>
+        <v>420</v>
       </c>
       <c r="G87">
-        <v>6346709</v>
+        <v>6346712</v>
       </c>
       <c r="H87" t="s">
         <v>24</v>
@@ -7320,7 +7375,7 @@
         <v>5</v>
       </c>
       <c r="K87">
-        <v>6346709</v>
+        <v>6346712</v>
       </c>
       <c r="L87" t="s">
         <v>25</v>
@@ -7344,13 +7399,13 @@
         <v>26</v>
       </c>
       <c r="S87">
-        <v>4321939</v>
+        <v>1758752</v>
       </c>
       <c r="T87">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="88" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>20</v>
       </c>
@@ -7364,16 +7419,16 @@
         <v>54</v>
       </c>
       <c r="E88" t="s">
-        <v>121</v>
+        <v>419</v>
       </c>
       <c r="F88" t="s">
-        <v>122</v>
+        <v>420</v>
       </c>
       <c r="G88">
-        <v>6346709</v>
+        <v>6346749</v>
       </c>
       <c r="H88" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="I88">
         <v>1</v>
@@ -7382,7 +7437,7 @@
         <v>5</v>
       </c>
       <c r="K88">
-        <v>6346709</v>
+        <v>6346749</v>
       </c>
       <c r="L88" t="s">
         <v>25</v>
@@ -7406,13 +7461,13 @@
         <v>26</v>
       </c>
       <c r="S88">
-        <v>4321939</v>
+        <v>1758752</v>
       </c>
       <c r="T88">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="89" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>20</v>
       </c>
@@ -7474,7 +7529,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>20</v>
       </c>
@@ -7536,7 +7591,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>20</v>
       </c>
@@ -7598,7 +7653,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>20</v>
       </c>
@@ -7660,7 +7715,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>20</v>
       </c>
@@ -7722,7 +7777,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>20</v>
       </c>
@@ -7784,7 +7839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>20</v>
       </c>
@@ -7846,7 +7901,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>20</v>
       </c>
@@ -7908,7 +7963,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
         <v>20</v>
       </c>
@@ -7970,7 +8025,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
         <v>20</v>
       </c>
@@ -8032,7 +8087,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
         <v>20</v>
       </c>
@@ -8094,7 +8149,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>20</v>
       </c>
@@ -8156,7 +8211,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
         <v>20</v>
       </c>
@@ -8218,7 +8273,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
         <v>20</v>
       </c>
@@ -8280,7 +8335,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
         <v>20</v>
       </c>
@@ -8342,7 +8397,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
         <v>20</v>
       </c>
@@ -8404,7 +8459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
         <v>20</v>
       </c>
@@ -8466,7 +8521,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
         <v>20</v>
       </c>
@@ -8528,7 +8583,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
         <v>20</v>
       </c>
@@ -8542,13 +8597,13 @@
         <v>52</v>
       </c>
       <c r="E107" t="s">
-        <v>138</v>
+        <v>401</v>
       </c>
       <c r="F107" t="s">
-        <v>139</v>
+        <v>402</v>
       </c>
       <c r="G107">
-        <v>6346723</v>
+        <v>6346713</v>
       </c>
       <c r="H107" t="s">
         <v>24</v>
@@ -8560,7 +8615,7 @@
         <v>4</v>
       </c>
       <c r="K107">
-        <v>6346723</v>
+        <v>6346713</v>
       </c>
       <c r="L107" t="s">
         <v>25</v>
@@ -8584,13 +8639,13 @@
         <v>26</v>
       </c>
       <c r="S107">
-        <v>3218866</v>
+        <v>1099807</v>
       </c>
       <c r="T107">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="108" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
         <v>20</v>
       </c>
@@ -8604,13 +8659,13 @@
         <v>52</v>
       </c>
       <c r="E108" t="s">
-        <v>138</v>
+        <v>401</v>
       </c>
       <c r="F108" t="s">
-        <v>139</v>
+        <v>402</v>
       </c>
       <c r="G108">
-        <v>6346753</v>
+        <v>6346750</v>
       </c>
       <c r="H108" t="s">
         <v>77</v>
@@ -8622,7 +8677,7 @@
         <v>4</v>
       </c>
       <c r="K108">
-        <v>6346753</v>
+        <v>6346750</v>
       </c>
       <c r="L108" t="s">
         <v>25</v>
@@ -8646,13 +8701,13 @@
         <v>26</v>
       </c>
       <c r="S108">
-        <v>3218866</v>
+        <v>1099807</v>
       </c>
       <c r="T108">
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
         <v>20</v>
       </c>
@@ -8666,13 +8721,13 @@
         <v>54</v>
       </c>
       <c r="E109" t="s">
-        <v>138</v>
+        <v>401</v>
       </c>
       <c r="F109" t="s">
-        <v>139</v>
+        <v>402</v>
       </c>
       <c r="G109">
-        <v>6346753</v>
+        <v>6346750</v>
       </c>
       <c r="H109" t="s">
         <v>77</v>
@@ -8684,7 +8739,7 @@
         <v>4</v>
       </c>
       <c r="K109">
-        <v>6346753</v>
+        <v>6346750</v>
       </c>
       <c r="L109" t="s">
         <v>25</v>
@@ -8708,13 +8763,13 @@
         <v>26</v>
       </c>
       <c r="S109">
-        <v>3218866</v>
+        <v>1099807</v>
       </c>
       <c r="T109">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="110" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
         <v>20</v>
       </c>
@@ -8776,7 +8831,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="111" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
         <v>20</v>
       </c>
@@ -8838,7 +8893,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="112" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
         <v>20</v>
       </c>
@@ -8900,7 +8955,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
         <v>20</v>
       </c>
@@ -8962,7 +9017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
         <v>20</v>
       </c>
@@ -9024,7 +9079,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="115" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
         <v>20</v>
       </c>
@@ -9086,7 +9141,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="116" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
         <v>20</v>
       </c>
@@ -9148,7 +9203,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="117" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
         <v>20</v>
       </c>
@@ -9210,7 +9265,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="118" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
         <v>20</v>
       </c>
@@ -9272,7 +9327,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="119" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
         <v>20</v>
       </c>
@@ -9334,7 +9389,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="120" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
         <v>20</v>
       </c>
@@ -9396,7 +9451,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="121" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
         <v>20</v>
       </c>
@@ -9458,7 +9513,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
         <v>20</v>
       </c>
@@ -9520,7 +9575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
         <v>20</v>
       </c>
@@ -9582,7 +9637,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="124" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
         <v>20</v>
       </c>
@@ -9644,7 +9699,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="125" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
         <v>20</v>
       </c>
@@ -9706,7 +9761,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="126" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
         <v>20</v>
       </c>
@@ -9768,7 +9823,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
         <v>20</v>
       </c>
@@ -9830,7 +9885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
         <v>20</v>
       </c>
@@ -9892,7 +9947,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
         <v>20</v>
       </c>
@@ -9954,7 +10009,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="130" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
         <v>20</v>
       </c>
@@ -10016,7 +10071,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="131" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
         <v>20</v>
       </c>
@@ -10078,7 +10133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
         <v>20</v>
       </c>
@@ -10140,7 +10195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
         <v>20</v>
       </c>
@@ -10202,7 +10257,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="134" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
         <v>20</v>
       </c>
@@ -10264,7 +10319,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="135" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
         <v>20</v>
       </c>
@@ -10326,7 +10381,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
         <v>20</v>
       </c>
@@ -10388,7 +10443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
         <v>20</v>
       </c>
@@ -10450,7 +10505,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="138" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
         <v>20</v>
       </c>
@@ -10512,7 +10567,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="139" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
         <v>20</v>
       </c>
@@ -10574,7 +10629,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="140" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
         <v>20</v>
       </c>
@@ -10636,7 +10691,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="141" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
         <v>20</v>
       </c>
@@ -10698,7 +10753,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="142" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
         <v>20</v>
       </c>
@@ -10760,7 +10815,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="143" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
         <v>20</v>
       </c>
@@ -10822,7 +10877,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="144" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
         <v>20</v>
       </c>
@@ -10884,7 +10939,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
         <v>20</v>
       </c>
@@ -10946,7 +11001,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="146" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
         <v>20</v>
       </c>
@@ -11008,7 +11063,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="147" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
         <v>20</v>
       </c>
@@ -11070,7 +11125,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="148" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
         <v>20</v>
       </c>
@@ -11132,7 +11187,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="149" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
         <v>20</v>
       </c>
@@ -11194,7 +11249,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="150" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
         <v>20</v>
       </c>
@@ -11256,7 +11311,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="151" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
         <v>20</v>
       </c>
@@ -11318,7 +11373,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="152" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A152" t="s">
         <v>20</v>
       </c>
@@ -11380,7 +11435,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="153" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
         <v>20</v>
       </c>
@@ -11442,7 +11497,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="154" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
         <v>20</v>
       </c>
@@ -11504,7 +11559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
         <v>20</v>
       </c>
@@ -11566,7 +11621,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="156" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
         <v>20</v>
       </c>
@@ -11628,7 +11683,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="157" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A157" t="s">
         <v>20</v>
       </c>
@@ -11690,7 +11745,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="158" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
         <v>20</v>
       </c>
@@ -11752,7 +11807,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="159" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A159" t="s">
         <v>20</v>
       </c>
@@ -11814,7 +11869,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="160" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
         <v>20</v>
       </c>
@@ -11876,7 +11931,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="161" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
         <v>20</v>
       </c>
@@ -11938,7 +11993,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="162" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
         <v>20</v>
       </c>
@@ -12000,7 +12055,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="163" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
         <v>20</v>
       </c>
@@ -12062,7 +12117,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="164" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A164" t="s">
         <v>20</v>
       </c>
@@ -12124,7 +12179,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="165" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
         <v>20</v>
       </c>
@@ -12186,7 +12241,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="166" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
         <v>20</v>
       </c>
@@ -12248,7 +12303,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="167" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A167" t="s">
         <v>20</v>
       </c>
@@ -12310,7 +12365,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="168" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A168" t="s">
         <v>20</v>
       </c>
@@ -12372,7 +12427,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="169" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
         <v>20</v>
       </c>
@@ -12434,7 +12489,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="170" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A170" t="s">
         <v>20</v>
       </c>
@@ -12496,7 +12551,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="171" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A171" t="s">
         <v>20</v>
       </c>
@@ -12558,7 +12613,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="172" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
         <v>20</v>
       </c>
@@ -12620,7 +12675,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="173" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A173" t="s">
         <v>20</v>
       </c>
@@ -12682,7 +12737,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="174" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A174" t="s">
         <v>20</v>
       </c>
@@ -12744,7 +12799,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="175" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A175" t="s">
         <v>20</v>
       </c>
@@ -12752,19 +12807,19 @@
         <v>8</v>
       </c>
       <c r="C175">
-        <v>39</v>
+        <v>808</v>
       </c>
       <c r="D175" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E175" t="s">
-        <v>170</v>
+        <v>423</v>
       </c>
       <c r="F175" t="s">
-        <v>171</v>
+        <v>424</v>
       </c>
       <c r="G175">
-        <v>6346716</v>
+        <v>6346726</v>
       </c>
       <c r="H175" t="s">
         <v>24</v>
@@ -12776,7 +12831,7 @@
         <v>5</v>
       </c>
       <c r="K175">
-        <v>6346716</v>
+        <v>6346726</v>
       </c>
       <c r="L175" t="s">
         <v>25</v>
@@ -12800,13 +12855,13 @@
         <v>26</v>
       </c>
       <c r="S175">
-        <v>2117533</v>
+        <v>3013004</v>
       </c>
       <c r="T175">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="176" spans="1:20" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="176" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A176" t="s">
         <v>20</v>
       </c>
@@ -12814,22 +12869,22 @@
         <v>8</v>
       </c>
       <c r="C176">
-        <v>808</v>
+        <v>39</v>
       </c>
       <c r="D176" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E176" t="s">
-        <v>170</v>
+        <v>423</v>
       </c>
       <c r="F176" t="s">
-        <v>171</v>
+        <v>424</v>
       </c>
       <c r="G176">
-        <v>6346754</v>
+        <v>6346726</v>
       </c>
       <c r="H176" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="I176">
         <v>1</v>
@@ -12838,7 +12893,7 @@
         <v>5</v>
       </c>
       <c r="K176">
-        <v>6346754</v>
+        <v>6346726</v>
       </c>
       <c r="L176" t="s">
         <v>25</v>
@@ -12862,13 +12917,13 @@
         <v>26</v>
       </c>
       <c r="S176">
-        <v>2814410</v>
+        <v>3013004</v>
       </c>
       <c r="T176">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="177" spans="1:20" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="177" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A177" t="s">
         <v>20</v>
       </c>
@@ -12882,13 +12937,13 @@
         <v>54</v>
       </c>
       <c r="E177" t="s">
-        <v>170</v>
+        <v>99</v>
       </c>
       <c r="F177" t="s">
-        <v>171</v>
+        <v>100</v>
       </c>
       <c r="G177">
-        <v>6357008</v>
+        <v>6346752</v>
       </c>
       <c r="H177" t="s">
         <v>77</v>
@@ -12900,10 +12955,10 @@
         <v>5</v>
       </c>
       <c r="K177">
-        <v>6357008</v>
+        <v>6346752</v>
       </c>
       <c r="L177" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="M177">
         <v>3</v>
@@ -12924,13 +12979,13 @@
         <v>26</v>
       </c>
       <c r="S177">
-        <v>3041802</v>
+        <v>3218866</v>
       </c>
       <c r="T177">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="178" spans="1:20" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="178" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A178" t="s">
         <v>20</v>
       </c>
@@ -12992,7 +13047,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="179" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A179" t="s">
         <v>20</v>
       </c>
@@ -13054,7 +13109,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="180" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A180" t="s">
         <v>20</v>
       </c>
@@ -13116,7 +13171,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="181" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
         <v>20</v>
       </c>
@@ -13178,7 +13233,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="182" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A182" t="s">
         <v>20</v>
       </c>
@@ -13240,7 +13295,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="183" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A183" t="s">
         <v>20</v>
       </c>
@@ -13302,7 +13357,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="184" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A184" t="s">
         <v>20</v>
       </c>
@@ -13364,7 +13419,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="185" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A185" t="s">
         <v>20</v>
       </c>
@@ -13426,7 +13481,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="186" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A186" t="s">
         <v>20</v>
       </c>
@@ -13488,7 +13543,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="187" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A187" t="s">
         <v>20</v>
       </c>
@@ -13550,7 +13605,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="188" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A188" t="s">
         <v>20</v>
       </c>
@@ -13612,7 +13667,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="189" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A189" t="s">
         <v>20</v>
       </c>
@@ -13674,7 +13729,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="190" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
         <v>20</v>
       </c>
@@ -13736,7 +13791,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="191" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A191" t="s">
         <v>20</v>
       </c>
@@ -13798,7 +13853,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="192" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A192" t="s">
         <v>20</v>
       </c>
@@ -13860,7 +13915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A193" t="s">
         <v>20</v>
       </c>
@@ -13922,7 +13977,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="194" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A194" t="s">
         <v>20</v>
       </c>
@@ -13984,7 +14039,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="195" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A195" t="s">
         <v>20</v>
       </c>
@@ -13998,13 +14053,13 @@
         <v>52</v>
       </c>
       <c r="E195" t="s">
-        <v>202</v>
+        <v>99</v>
       </c>
       <c r="F195" t="s">
-        <v>203</v>
+        <v>100</v>
       </c>
       <c r="G195">
-        <v>6346717</v>
+        <v>6346715</v>
       </c>
       <c r="H195" t="s">
         <v>24</v>
@@ -14016,7 +14071,7 @@
         <v>5</v>
       </c>
       <c r="K195">
-        <v>6346717</v>
+        <v>6346715</v>
       </c>
       <c r="L195" t="s">
         <v>25</v>
@@ -14043,10 +14098,10 @@
         <v>3218866</v>
       </c>
       <c r="T195">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="196" spans="1:20" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="196" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A196" t="s">
         <v>20</v>
       </c>
@@ -14054,19 +14109,19 @@
         <v>8</v>
       </c>
       <c r="C196">
-        <v>808</v>
+        <v>39</v>
       </c>
       <c r="D196" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E196" t="s">
-        <v>202</v>
+        <v>138</v>
       </c>
       <c r="F196" t="s">
-        <v>203</v>
+        <v>139</v>
       </c>
       <c r="G196">
-        <v>6346717</v>
+        <v>6346723</v>
       </c>
       <c r="H196" t="s">
         <v>24</v>
@@ -14075,16 +14130,16 @@
         <v>1</v>
       </c>
       <c r="J196">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K196">
-        <v>6346717</v>
+        <v>6346723</v>
       </c>
       <c r="L196" t="s">
         <v>25</v>
       </c>
       <c r="M196">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N196">
         <v>0</v>
@@ -14093,10 +14148,10 @@
         <v>4</v>
       </c>
       <c r="P196">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q196">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R196" t="s">
         <v>26</v>
@@ -14105,10 +14160,10 @@
         <v>3218866</v>
       </c>
       <c r="T196">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="197" spans="1:20" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="197" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A197" t="s">
         <v>20</v>
       </c>
@@ -14170,7 +14225,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="198" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A198" t="s">
         <v>20</v>
       </c>
@@ -14232,7 +14287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A199" t="s">
         <v>20</v>
       </c>
@@ -14294,7 +14349,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="200" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A200" t="s">
         <v>20</v>
       </c>
@@ -14356,7 +14411,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="201" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A201" t="s">
         <v>20</v>
       </c>
@@ -14418,7 +14473,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="202" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A202" t="s">
         <v>20</v>
       </c>
@@ -14480,7 +14535,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="203" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A203" t="s">
         <v>20</v>
       </c>
@@ -14542,7 +14597,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="204" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A204" t="s">
         <v>20</v>
       </c>
@@ -14604,7 +14659,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="205" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A205" t="s">
         <v>20</v>
       </c>
@@ -14666,7 +14721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A206" t="s">
         <v>20</v>
       </c>
@@ -14728,7 +14783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A207" t="s">
         <v>20</v>
       </c>
@@ -14790,7 +14845,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A208" t="s">
         <v>20</v>
       </c>
@@ -14852,7 +14907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A209" t="s">
         <v>20</v>
       </c>
@@ -14914,7 +14969,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="210" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A210" t="s">
         <v>20</v>
       </c>
@@ -14976,7 +15031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A211" t="s">
         <v>20</v>
       </c>
@@ -15038,7 +15093,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="212" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A212" t="s">
         <v>20</v>
       </c>
@@ -15100,7 +15155,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="213" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A213" t="s">
         <v>20</v>
       </c>
@@ -15162,7 +15217,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="214" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A214" t="s">
         <v>20</v>
       </c>
@@ -15224,7 +15279,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="215" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A215" t="s">
         <v>20</v>
       </c>
@@ -15286,7 +15341,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="216" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A216" t="s">
         <v>20</v>
       </c>
@@ -15348,7 +15403,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="217" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A217" t="s">
         <v>20</v>
       </c>
@@ -15410,7 +15465,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="218" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A218" t="s">
         <v>20</v>
       </c>
@@ -15472,7 +15527,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="219" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A219" t="s">
         <v>20</v>
       </c>
@@ -15534,7 +15589,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="220" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A220" t="s">
         <v>20</v>
       </c>
@@ -15596,7 +15651,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="221" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A221" t="s">
         <v>20</v>
       </c>
@@ -15658,7 +15713,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="222" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A222" t="s">
         <v>20</v>
       </c>
@@ -15720,7 +15775,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="223" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A223" t="s">
         <v>20</v>
       </c>
@@ -15782,7 +15837,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="224" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A224" t="s">
         <v>20</v>
       </c>
@@ -15844,7 +15899,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="225" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A225" t="s">
         <v>20</v>
       </c>
@@ -15906,7 +15961,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="226" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A226" t="s">
         <v>20</v>
       </c>
@@ -15968,7 +16023,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="227" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A227" t="s">
         <v>20</v>
       </c>
@@ -16030,7 +16085,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="228" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A228" t="s">
         <v>20</v>
       </c>
@@ -16092,7 +16147,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="229" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A229" t="s">
         <v>20</v>
       </c>
@@ -16154,7 +16209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A230" t="s">
         <v>20</v>
       </c>
@@ -16162,31 +16217,31 @@
         <v>8</v>
       </c>
       <c r="C230">
-        <v>808</v>
+        <v>39</v>
       </c>
       <c r="D230" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E230" t="s">
-        <v>250</v>
+        <v>138</v>
       </c>
       <c r="F230" t="s">
-        <v>251</v>
+        <v>139</v>
       </c>
       <c r="G230">
-        <v>6346949</v>
+        <v>6346753</v>
       </c>
       <c r="H230" t="s">
         <v>77</v>
       </c>
       <c r="I230">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J230">
         <v>4</v>
       </c>
       <c r="K230">
-        <v>6346949</v>
+        <v>6346753</v>
       </c>
       <c r="L230" t="s">
         <v>25</v>
@@ -16204,19 +16259,19 @@
         <v>0</v>
       </c>
       <c r="Q230">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R230" t="s">
         <v>26</v>
       </c>
       <c r="S230">
-        <v>3261519</v>
+        <v>3218866</v>
       </c>
       <c r="T230">
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A231" t="s">
         <v>20</v>
       </c>
@@ -16224,22 +16279,22 @@
         <v>8</v>
       </c>
       <c r="C231">
-        <v>39</v>
+        <v>808</v>
       </c>
       <c r="D231" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E231" t="s">
-        <v>250</v>
+        <v>138</v>
       </c>
       <c r="F231" t="s">
-        <v>251</v>
+        <v>139</v>
       </c>
       <c r="G231">
-        <v>6346721</v>
+        <v>6346753</v>
       </c>
       <c r="H231" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="I231">
         <v>1</v>
@@ -16248,7 +16303,7 @@
         <v>4</v>
       </c>
       <c r="K231">
-        <v>6346721</v>
+        <v>6346753</v>
       </c>
       <c r="L231" t="s">
         <v>25</v>
@@ -16266,7 +16321,7 @@
         <v>0</v>
       </c>
       <c r="Q231">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R231" t="s">
         <v>26</v>
@@ -16275,10 +16330,10 @@
         <v>3218866</v>
       </c>
       <c r="T231">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="232" spans="1:20" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="232" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A232" t="s">
         <v>20</v>
       </c>
@@ -16286,37 +16341,37 @@
         <v>8</v>
       </c>
       <c r="C232">
-        <v>808</v>
+        <v>39</v>
       </c>
       <c r="D232" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E232" t="s">
-        <v>250</v>
+        <v>170</v>
       </c>
       <c r="F232" t="s">
-        <v>251</v>
+        <v>171</v>
       </c>
       <c r="G232">
-        <v>6346951</v>
+        <v>6346716</v>
       </c>
       <c r="H232" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="I232">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J232">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K232">
-        <v>6346951</v>
+        <v>6346716</v>
       </c>
       <c r="L232" t="s">
         <v>25</v>
       </c>
       <c r="M232">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N232">
         <v>0</v>
@@ -16325,22 +16380,22 @@
         <v>4</v>
       </c>
       <c r="P232">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q232">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R232" t="s">
         <v>26</v>
       </c>
       <c r="S232">
-        <v>3041802</v>
+        <v>2117533</v>
       </c>
       <c r="T232">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="233" spans="1:20" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="233" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A233" t="s">
         <v>20</v>
       </c>
@@ -16348,37 +16403,37 @@
         <v>8</v>
       </c>
       <c r="C233">
-        <v>39</v>
+        <v>808</v>
       </c>
       <c r="D233" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E233" t="s">
-        <v>250</v>
+        <v>170</v>
       </c>
       <c r="F233" t="s">
-        <v>251</v>
+        <v>171</v>
       </c>
       <c r="G233">
-        <v>6346946</v>
+        <v>6346754</v>
       </c>
       <c r="H233" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="I233">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J233">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K233">
-        <v>6346946</v>
+        <v>6346754</v>
       </c>
       <c r="L233" t="s">
         <v>25</v>
       </c>
       <c r="M233">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N233">
         <v>0</v>
@@ -16387,22 +16442,22 @@
         <v>4</v>
       </c>
       <c r="P233">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q233">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R233" t="s">
         <v>26</v>
       </c>
       <c r="S233">
-        <v>3261519</v>
+        <v>2814410</v>
       </c>
       <c r="T233">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="234" spans="1:20" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="234" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A234" t="s">
         <v>20</v>
       </c>
@@ -16410,37 +16465,37 @@
         <v>8</v>
       </c>
       <c r="C234">
-        <v>39</v>
+        <v>808</v>
       </c>
       <c r="D234" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E234" t="s">
-        <v>250</v>
+        <v>170</v>
       </c>
       <c r="F234" t="s">
-        <v>251</v>
+        <v>171</v>
       </c>
       <c r="G234">
-        <v>6346947</v>
+        <v>6357008</v>
       </c>
       <c r="H234" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="I234">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J234">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K234">
-        <v>6346947</v>
+        <v>6357008</v>
       </c>
       <c r="L234" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="M234">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N234">
         <v>0</v>
@@ -16449,22 +16504,22 @@
         <v>4</v>
       </c>
       <c r="P234">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q234">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R234" t="s">
         <v>26</v>
       </c>
       <c r="S234">
-        <v>2814410</v>
+        <v>3041802</v>
       </c>
       <c r="T234">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="235" spans="1:20" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A235" t="s">
         <v>20</v>
       </c>
@@ -16478,31 +16533,31 @@
         <v>52</v>
       </c>
       <c r="E235" t="s">
-        <v>250</v>
+        <v>202</v>
       </c>
       <c r="F235" t="s">
-        <v>251</v>
+        <v>203</v>
       </c>
       <c r="G235">
-        <v>6346948</v>
+        <v>6346717</v>
       </c>
       <c r="H235" t="s">
         <v>24</v>
       </c>
       <c r="I235">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J235">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K235">
-        <v>6346948</v>
+        <v>6346717</v>
       </c>
       <c r="L235" t="s">
         <v>25</v>
       </c>
       <c r="M235">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N235">
         <v>0</v>
@@ -16511,22 +16566,22 @@
         <v>4</v>
       </c>
       <c r="P235">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q235">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R235" t="s">
         <v>26</v>
       </c>
       <c r="S235">
-        <v>3041802</v>
+        <v>3218866</v>
       </c>
       <c r="T235">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="236" spans="1:20" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="236" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A236" t="s">
         <v>20</v>
       </c>
@@ -16540,31 +16595,31 @@
         <v>54</v>
       </c>
       <c r="E236" t="s">
-        <v>250</v>
+        <v>202</v>
       </c>
       <c r="F236" t="s">
-        <v>251</v>
+        <v>203</v>
       </c>
       <c r="G236">
-        <v>6346950</v>
+        <v>6346717</v>
       </c>
       <c r="H236" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="I236">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J236">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K236">
-        <v>6346950</v>
+        <v>6346717</v>
       </c>
       <c r="L236" t="s">
         <v>25</v>
       </c>
       <c r="M236">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N236">
         <v>0</v>
@@ -16573,22 +16628,22 @@
         <v>4</v>
       </c>
       <c r="P236">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q236">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R236" t="s">
         <v>26</v>
       </c>
       <c r="S236">
-        <v>2814410</v>
+        <v>3218866</v>
       </c>
       <c r="T236">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="237" spans="1:20" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="237" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A237" t="s">
         <v>20</v>
       </c>
@@ -16650,7 +16705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A238" t="s">
         <v>20</v>
       </c>
@@ -16712,7 +16767,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="239" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A239" t="s">
         <v>20</v>
       </c>
@@ -16774,7 +16829,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="240" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A240" t="s">
         <v>20</v>
       </c>
@@ -16836,7 +16891,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="241" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A241" t="s">
         <v>20</v>
       </c>
@@ -16898,7 +16953,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="242" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A242" t="s">
         <v>20</v>
       </c>
@@ -16960,7 +17015,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="243" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A243" t="s">
         <v>20</v>
       </c>
@@ -17022,7 +17077,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="244" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A244" t="s">
         <v>20</v>
       </c>
@@ -17084,7 +17139,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="245" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A245" t="s">
         <v>20</v>
       </c>
@@ -17146,7 +17201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A246" t="s">
         <v>20</v>
       </c>
@@ -17208,7 +17263,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="247" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A247" t="s">
         <v>20</v>
       </c>
@@ -17270,7 +17325,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="248" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A248" t="s">
         <v>20</v>
       </c>
@@ -17332,7 +17387,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="249" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A249" t="s">
         <v>20</v>
       </c>
@@ -17394,7 +17449,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="250" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A250" t="s">
         <v>20</v>
       </c>
@@ -17456,7 +17511,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="251" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A251" t="s">
         <v>20</v>
       </c>
@@ -17518,7 +17573,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="252" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A252" t="s">
         <v>20</v>
       </c>
@@ -17580,7 +17635,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="253" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A253" t="s">
         <v>20</v>
       </c>
@@ -17642,7 +17697,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="254" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A254" t="s">
         <v>20</v>
       </c>
@@ -17656,13 +17711,13 @@
         <v>52</v>
       </c>
       <c r="E254" t="s">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="F254" t="s">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="G254">
-        <v>6346708</v>
+        <v>6346718</v>
       </c>
       <c r="H254" t="s">
         <v>24</v>
@@ -17671,16 +17726,16 @@
         <v>1</v>
       </c>
       <c r="J254">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K254">
-        <v>6346708</v>
+        <v>6346718</v>
       </c>
       <c r="L254" t="s">
         <v>25</v>
       </c>
       <c r="M254">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N254">
         <v>0</v>
@@ -17689,7 +17744,7 @@
         <v>4</v>
       </c>
       <c r="P254">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q254">
         <v>0</v>
@@ -17698,13 +17753,13 @@
         <v>26</v>
       </c>
       <c r="S254">
-        <v>3415337</v>
+        <v>1932179</v>
       </c>
       <c r="T254">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="255" spans="1:20" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="255" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A255" t="s">
         <v>20</v>
       </c>
@@ -17718,13 +17773,13 @@
         <v>54</v>
       </c>
       <c r="E255" t="s">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="F255" t="s">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="G255">
-        <v>6346708</v>
+        <v>6346718</v>
       </c>
       <c r="H255" t="s">
         <v>24</v>
@@ -17733,16 +17788,16 @@
         <v>1</v>
       </c>
       <c r="J255">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K255">
-        <v>6346708</v>
+        <v>6346718</v>
       </c>
       <c r="L255" t="s">
         <v>25</v>
       </c>
       <c r="M255">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N255">
         <v>0</v>
@@ -17751,7 +17806,7 @@
         <v>4</v>
       </c>
       <c r="P255">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q255">
         <v>0</v>
@@ -17760,13 +17815,13 @@
         <v>26</v>
       </c>
       <c r="S255">
-        <v>3415337</v>
+        <v>1932179</v>
       </c>
       <c r="T255">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="256" spans="1:20" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="256" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A256" t="s">
         <v>20</v>
       </c>
@@ -17828,7 +17883,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="257" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A257" t="s">
         <v>20</v>
       </c>
@@ -17890,7 +17945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A258" t="s">
         <v>20</v>
       </c>
@@ -17952,7 +18007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A259" t="s">
         <v>20</v>
       </c>
@@ -18014,7 +18069,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="260" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A260" t="s">
         <v>20</v>
       </c>
@@ -18076,7 +18131,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="261" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A261" t="s">
         <v>20</v>
       </c>
@@ -18138,7 +18193,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="262" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A262" t="s">
         <v>20</v>
       </c>
@@ -18200,7 +18255,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="263" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A263" t="s">
         <v>20</v>
       </c>
@@ -18262,7 +18317,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="264" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A264" t="s">
         <v>20</v>
       </c>
@@ -18324,7 +18379,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="265" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A265" t="s">
         <v>20</v>
       </c>
@@ -18386,7 +18441,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="266" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A266" t="s">
         <v>20</v>
       </c>
@@ -18448,7 +18503,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="267" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A267" t="s">
         <v>20</v>
       </c>
@@ -18510,7 +18565,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="268" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A268" t="s">
         <v>20</v>
       </c>
@@ -18518,22 +18573,22 @@
         <v>8</v>
       </c>
       <c r="C268">
-        <v>39</v>
+        <v>808</v>
       </c>
       <c r="D268" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E268" t="s">
-        <v>294</v>
+        <v>75</v>
       </c>
       <c r="F268" t="s">
-        <v>295</v>
+        <v>76</v>
       </c>
       <c r="G268">
-        <v>6346718</v>
+        <v>6346757</v>
       </c>
       <c r="H268" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="I268">
         <v>1</v>
@@ -18542,7 +18597,7 @@
         <v>2</v>
       </c>
       <c r="K268">
-        <v>6346718</v>
+        <v>6346757</v>
       </c>
       <c r="L268" t="s">
         <v>25</v>
@@ -18566,13 +18621,13 @@
         <v>26</v>
       </c>
       <c r="S268">
-        <v>1932179</v>
+        <v>6792717</v>
       </c>
       <c r="T268">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="269" spans="1:20" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="269" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A269" t="s">
         <v>20</v>
       </c>
@@ -18580,19 +18635,19 @@
         <v>8</v>
       </c>
       <c r="C269">
-        <v>808</v>
+        <v>39</v>
       </c>
       <c r="D269" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E269" t="s">
-        <v>294</v>
+        <v>75</v>
       </c>
       <c r="F269" t="s">
-        <v>295</v>
+        <v>76</v>
       </c>
       <c r="G269">
-        <v>6346718</v>
+        <v>6346719</v>
       </c>
       <c r="H269" t="s">
         <v>24</v>
@@ -18604,7 +18659,7 @@
         <v>2</v>
       </c>
       <c r="K269">
-        <v>6346718</v>
+        <v>6346719</v>
       </c>
       <c r="L269" t="s">
         <v>25</v>
@@ -18628,13 +18683,13 @@
         <v>26</v>
       </c>
       <c r="S269">
-        <v>1932179</v>
+        <v>1635809</v>
       </c>
       <c r="T269">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="270" spans="1:20" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="270" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A270" t="s">
         <v>20</v>
       </c>
@@ -18696,7 +18751,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="271" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A271" t="s">
         <v>20</v>
       </c>
@@ -18758,7 +18813,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="272" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A272" t="s">
         <v>20</v>
       </c>
@@ -18820,7 +18875,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="273" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A273" t="s">
         <v>20</v>
       </c>
@@ -18882,7 +18937,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="274" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A274" t="s">
         <v>20</v>
       </c>
@@ -18944,7 +18999,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="275" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A275" t="s">
         <v>20</v>
       </c>
@@ -19006,7 +19061,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="276" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A276" t="s">
         <v>20</v>
       </c>
@@ -19068,7 +19123,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="277" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A277" t="s">
         <v>20</v>
       </c>
@@ -19130,7 +19185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A278" t="s">
         <v>20</v>
       </c>
@@ -19192,7 +19247,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="279" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A279" t="s">
         <v>20</v>
       </c>
@@ -19254,7 +19309,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="280" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A280" t="s">
         <v>20</v>
       </c>
@@ -19316,7 +19371,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="281" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A281" t="s">
         <v>20</v>
       </c>
@@ -19378,7 +19433,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="282" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A282" t="s">
         <v>20</v>
       </c>
@@ -19440,7 +19495,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="283" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A283" t="s">
         <v>20</v>
       </c>
@@ -19502,7 +19557,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="284" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A284" t="s">
         <v>20</v>
       </c>
@@ -19564,7 +19619,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="285" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A285" t="s">
         <v>20</v>
       </c>
@@ -19626,7 +19681,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="286" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A286" t="s">
         <v>20</v>
       </c>
@@ -19688,7 +19743,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="287" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A287" t="s">
         <v>20</v>
       </c>
@@ -19750,7 +19805,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="288" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A288" t="s">
         <v>20</v>
       </c>
@@ -19812,7 +19867,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="289" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A289" t="s">
         <v>20</v>
       </c>
@@ -19874,7 +19929,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="290" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A290" t="s">
         <v>20</v>
       </c>
@@ -19936,7 +19991,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="291" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A291" t="s">
         <v>20</v>
       </c>
@@ -19998,7 +20053,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="292" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A292" t="s">
         <v>20</v>
       </c>
@@ -20060,7 +20115,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="293" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A293" t="s">
         <v>20</v>
       </c>
@@ -20122,7 +20177,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="294" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A294" t="s">
         <v>20</v>
       </c>
@@ -20184,7 +20239,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="295" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A295" t="s">
         <v>20</v>
       </c>
@@ -20246,7 +20301,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="296" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A296" t="s">
         <v>20</v>
       </c>
@@ -20308,7 +20363,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="297" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A297" t="s">
         <v>20</v>
       </c>
@@ -20370,7 +20425,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="298" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A298" t="s">
         <v>20</v>
       </c>
@@ -20432,7 +20487,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="299" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A299" t="s">
         <v>20</v>
       </c>
@@ -20494,7 +20549,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="300" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A300" t="s">
         <v>20</v>
       </c>
@@ -20556,7 +20611,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="301" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A301" t="s">
         <v>20</v>
       </c>
@@ -20618,7 +20673,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="302" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A302" t="s">
         <v>20</v>
       </c>
@@ -20680,7 +20735,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="303" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A303" t="s">
         <v>20</v>
       </c>
@@ -20742,7 +20797,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="304" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A304" t="s">
         <v>20</v>
       </c>
@@ -20804,7 +20859,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="305" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A305" t="s">
         <v>20</v>
       </c>
@@ -20866,7 +20921,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="306" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A306" t="s">
         <v>20</v>
       </c>
@@ -20928,7 +20983,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="307" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A307" t="s">
         <v>20</v>
       </c>
@@ -20990,7 +21045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="308" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A308" t="s">
         <v>20</v>
       </c>
@@ -21052,7 +21107,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="309" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A309" t="s">
         <v>20</v>
       </c>
@@ -21114,7 +21169,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="310" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A310" t="s">
         <v>20</v>
       </c>
@@ -21176,7 +21231,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="311" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A311" t="s">
         <v>20</v>
       </c>
@@ -21238,7 +21293,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="312" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A312" t="s">
         <v>20</v>
       </c>
@@ -21300,7 +21355,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="313" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A313" t="s">
         <v>20</v>
       </c>
@@ -21362,7 +21417,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="314" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A314" t="s">
         <v>20</v>
       </c>
@@ -21424,7 +21479,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="315" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A315" t="s">
         <v>20</v>
       </c>
@@ -21486,7 +21541,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="316" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A316" t="s">
         <v>20</v>
       </c>
@@ -21548,7 +21603,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="317" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A317" t="s">
         <v>20</v>
       </c>
@@ -21610,7 +21665,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="318" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A318" t="s">
         <v>20</v>
       </c>
@@ -21672,7 +21727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="319" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A319" t="s">
         <v>20</v>
       </c>
@@ -21734,7 +21789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="320" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A320" t="s">
         <v>20</v>
       </c>
@@ -21796,7 +21851,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="321" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A321" t="s">
         <v>20</v>
       </c>
@@ -21858,7 +21913,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="322" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A322" t="s">
         <v>20</v>
       </c>
@@ -21920,7 +21975,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="323" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A323" t="s">
         <v>20</v>
       </c>
@@ -21982,7 +22037,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="324" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A324" t="s">
         <v>20</v>
       </c>
@@ -22044,7 +22099,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="325" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A325" t="s">
         <v>20</v>
       </c>
@@ -22106,7 +22161,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="326" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A326" t="s">
         <v>20</v>
       </c>
@@ -22168,7 +22223,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="327" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A327" t="s">
         <v>20</v>
       </c>
@@ -22230,7 +22285,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="328" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A328" t="s">
         <v>20</v>
       </c>
@@ -22292,7 +22347,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="329" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A329" t="s">
         <v>20</v>
       </c>
@@ -22354,7 +22409,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="330" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A330" t="s">
         <v>20</v>
       </c>
@@ -22416,7 +22471,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="331" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A331" t="s">
         <v>20</v>
       </c>
@@ -22478,7 +22533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="332" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A332" t="s">
         <v>20</v>
       </c>
@@ -22540,7 +22595,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="333" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A333" t="s">
         <v>20</v>
       </c>
@@ -22602,7 +22657,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="334" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A334" t="s">
         <v>20</v>
       </c>
@@ -22664,7 +22719,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="335" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A335" t="s">
         <v>20</v>
       </c>
@@ -22726,7 +22781,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="336" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A336" t="s">
         <v>20</v>
       </c>
@@ -22788,7 +22843,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="337" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A337" t="s">
         <v>20</v>
       </c>
@@ -22850,7 +22905,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="338" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A338" t="s">
         <v>20</v>
       </c>
@@ -22912,7 +22967,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="339" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A339" t="s">
         <v>20</v>
       </c>
@@ -22974,7 +23029,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="340" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A340" t="s">
         <v>20</v>
       </c>
@@ -23036,7 +23091,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="341" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A341" t="s">
         <v>20</v>
       </c>
@@ -23098,7 +23153,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="342" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A342" t="s">
         <v>20</v>
       </c>
@@ -23160,7 +23215,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="343" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A343" t="s">
         <v>20</v>
       </c>
@@ -23222,7 +23277,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="344" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A344" t="s">
         <v>20</v>
       </c>
@@ -23236,13 +23291,13 @@
         <v>52</v>
       </c>
       <c r="E344" t="s">
-        <v>370</v>
+        <v>533</v>
       </c>
       <c r="F344" t="s">
-        <v>371</v>
+        <v>532</v>
       </c>
       <c r="G344">
-        <v>6351265</v>
+        <v>6346720</v>
       </c>
       <c r="H344" t="s">
         <v>24</v>
@@ -23251,16 +23306,16 @@
         <v>1</v>
       </c>
       <c r="J344">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K344">
-        <v>6351265</v>
+        <v>6346720</v>
       </c>
       <c r="L344" t="s">
         <v>25</v>
       </c>
       <c r="M344">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N344">
         <v>0</v>
@@ -23269,22 +23324,22 @@
         <v>4</v>
       </c>
       <c r="P344">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q344">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R344" t="s">
         <v>26</v>
       </c>
       <c r="S344">
-        <v>7208507</v>
+        <v>3473810</v>
       </c>
       <c r="T344">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="345" spans="1:20" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="345" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A345" t="s">
         <v>20</v>
       </c>
@@ -23292,37 +23347,37 @@
         <v>8</v>
       </c>
       <c r="C345">
-        <v>39</v>
+        <v>808</v>
       </c>
       <c r="D345" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E345" t="s">
-        <v>372</v>
+        <v>533</v>
       </c>
       <c r="F345" t="s">
-        <v>373</v>
+        <v>532</v>
       </c>
       <c r="G345">
-        <v>6359928</v>
+        <v>6346758</v>
       </c>
       <c r="H345" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="I345">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J345">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K345">
-        <v>6359928</v>
+        <v>6346758</v>
       </c>
       <c r="L345" t="s">
         <v>25</v>
       </c>
       <c r="M345">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N345">
         <v>0</v>
@@ -23331,22 +23386,22 @@
         <v>4</v>
       </c>
       <c r="P345">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q345">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R345" t="s">
         <v>26</v>
       </c>
       <c r="S345">
-        <v>1156444</v>
+        <v>3473810</v>
       </c>
       <c r="T345">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="346" spans="1:20" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="346" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A346" t="s">
         <v>20</v>
       </c>
@@ -23354,31 +23409,31 @@
         <v>8</v>
       </c>
       <c r="C346">
-        <v>39</v>
+        <v>808</v>
       </c>
       <c r="D346" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E346" t="s">
-        <v>372</v>
+        <v>250</v>
       </c>
       <c r="F346" t="s">
-        <v>373</v>
+        <v>251</v>
       </c>
       <c r="G346">
-        <v>6346941</v>
+        <v>6346949</v>
       </c>
       <c r="H346" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="I346">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J346">
         <v>4</v>
       </c>
       <c r="K346">
-        <v>6346941</v>
+        <v>6346949</v>
       </c>
       <c r="L346" t="s">
         <v>25</v>
@@ -23402,13 +23457,13 @@
         <v>26</v>
       </c>
       <c r="S346">
-        <v>4721220</v>
+        <v>3261519</v>
       </c>
       <c r="T346">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="347" spans="1:20" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="347" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A347" t="s">
         <v>20</v>
       </c>
@@ -23416,31 +23471,31 @@
         <v>8</v>
       </c>
       <c r="C347">
-        <v>808</v>
+        <v>39</v>
       </c>
       <c r="D347" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E347" t="s">
-        <v>372</v>
+        <v>250</v>
       </c>
       <c r="F347" t="s">
-        <v>373</v>
+        <v>251</v>
       </c>
       <c r="G347">
-        <v>6359930</v>
+        <v>6346721</v>
       </c>
       <c r="H347" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="I347">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J347">
         <v>4</v>
       </c>
       <c r="K347">
-        <v>6359930</v>
+        <v>6346721</v>
       </c>
       <c r="L347" t="s">
         <v>25</v>
@@ -23464,13 +23519,13 @@
         <v>26</v>
       </c>
       <c r="S347">
-        <v>1156444</v>
+        <v>3218866</v>
       </c>
       <c r="T347">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="348" spans="1:20" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="348" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A348" t="s">
         <v>20</v>
       </c>
@@ -23478,31 +23533,31 @@
         <v>8</v>
       </c>
       <c r="C348">
-        <v>39</v>
+        <v>808</v>
       </c>
       <c r="D348" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E348" t="s">
-        <v>372</v>
+        <v>250</v>
       </c>
       <c r="F348" t="s">
-        <v>373</v>
+        <v>251</v>
       </c>
       <c r="G348">
-        <v>6346939</v>
+        <v>6346951</v>
       </c>
       <c r="H348" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="I348">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J348">
         <v>4</v>
       </c>
       <c r="K348">
-        <v>6346939</v>
+        <v>6346951</v>
       </c>
       <c r="L348" t="s">
         <v>25</v>
@@ -23526,13 +23581,13 @@
         <v>26</v>
       </c>
       <c r="S348">
-        <v>1540100</v>
+        <v>3041802</v>
       </c>
       <c r="T348">
         <v>2</v>
       </c>
     </row>
-    <row r="349" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A349" t="s">
         <v>20</v>
       </c>
@@ -23540,31 +23595,31 @@
         <v>8</v>
       </c>
       <c r="C349">
-        <v>808</v>
+        <v>39</v>
       </c>
       <c r="D349" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E349" t="s">
-        <v>372</v>
+        <v>250</v>
       </c>
       <c r="F349" t="s">
-        <v>373</v>
+        <v>251</v>
       </c>
       <c r="G349">
-        <v>6346954</v>
+        <v>6346946</v>
       </c>
       <c r="H349" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="I349">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J349">
         <v>4</v>
       </c>
       <c r="K349">
-        <v>6346954</v>
+        <v>6346946</v>
       </c>
       <c r="L349" t="s">
         <v>25</v>
@@ -23588,13 +23643,13 @@
         <v>26</v>
       </c>
       <c r="S349">
-        <v>4721220</v>
+        <v>3261519</v>
       </c>
       <c r="T349">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="350" spans="1:20" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="350" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A350" t="s">
         <v>20</v>
       </c>
@@ -23608,25 +23663,25 @@
         <v>52</v>
       </c>
       <c r="E350" t="s">
-        <v>372</v>
+        <v>250</v>
       </c>
       <c r="F350" t="s">
-        <v>373</v>
+        <v>251</v>
       </c>
       <c r="G350">
-        <v>6346722</v>
+        <v>6346947</v>
       </c>
       <c r="H350" t="s">
         <v>24</v>
       </c>
       <c r="I350">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J350">
         <v>4</v>
       </c>
       <c r="K350">
-        <v>6346722</v>
+        <v>6346947</v>
       </c>
       <c r="L350" t="s">
         <v>25</v>
@@ -23650,13 +23705,13 @@
         <v>26</v>
       </c>
       <c r="S350">
-        <v>2117533</v>
+        <v>2814410</v>
       </c>
       <c r="T350">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="351" spans="1:20" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="351" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A351" t="s">
         <v>20</v>
       </c>
@@ -23670,25 +23725,25 @@
         <v>52</v>
       </c>
       <c r="E351" t="s">
-        <v>372</v>
+        <v>250</v>
       </c>
       <c r="F351" t="s">
-        <v>373</v>
+        <v>251</v>
       </c>
       <c r="G351">
-        <v>6346940</v>
+        <v>6346948</v>
       </c>
       <c r="H351" t="s">
         <v>24</v>
       </c>
       <c r="I351">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J351">
         <v>4</v>
       </c>
       <c r="K351">
-        <v>6346940</v>
+        <v>6346948</v>
       </c>
       <c r="L351" t="s">
         <v>25</v>
@@ -23712,13 +23767,13 @@
         <v>26</v>
       </c>
       <c r="S351">
-        <v>7208507</v>
+        <v>3041802</v>
       </c>
       <c r="T351">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="352" spans="1:20" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="352" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A352" t="s">
         <v>20</v>
       </c>
@@ -23726,31 +23781,31 @@
         <v>8</v>
       </c>
       <c r="C352">
-        <v>39</v>
+        <v>808</v>
       </c>
       <c r="D352" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E352" t="s">
-        <v>372</v>
+        <v>250</v>
       </c>
       <c r="F352" t="s">
-        <v>373</v>
+        <v>251</v>
       </c>
       <c r="G352">
-        <v>6346942</v>
+        <v>6346950</v>
       </c>
       <c r="H352" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="I352">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J352">
         <v>4</v>
       </c>
       <c r="K352">
-        <v>6346942</v>
+        <v>6346950</v>
       </c>
       <c r="L352" t="s">
         <v>25</v>
@@ -23774,13 +23829,13 @@
         <v>26</v>
       </c>
       <c r="S352">
-        <v>1121323</v>
+        <v>2814410</v>
       </c>
       <c r="T352">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="353" spans="1:20" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="353" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A353" t="s">
         <v>20</v>
       </c>
@@ -23788,10 +23843,10 @@
         <v>8</v>
       </c>
       <c r="C353">
-        <v>808</v>
+        <v>39</v>
       </c>
       <c r="D353" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E353" t="s">
         <v>372</v>
@@ -23800,19 +23855,19 @@
         <v>373</v>
       </c>
       <c r="G353">
-        <v>6346760</v>
+        <v>6359928</v>
       </c>
       <c r="H353" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="I353">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J353">
         <v>4</v>
       </c>
       <c r="K353">
-        <v>6346760</v>
+        <v>6359928</v>
       </c>
       <c r="L353" t="s">
         <v>25</v>
@@ -23836,13 +23891,13 @@
         <v>26</v>
       </c>
       <c r="S353">
-        <v>2117533</v>
+        <v>1156444</v>
       </c>
       <c r="T353">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="354" spans="1:20" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="354" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A354" t="s">
         <v>20</v>
       </c>
@@ -23862,19 +23917,19 @@
         <v>373</v>
       </c>
       <c r="G354">
-        <v>6346945</v>
+        <v>6346941</v>
       </c>
       <c r="H354" t="s">
         <v>24</v>
       </c>
       <c r="I354">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J354">
         <v>4</v>
       </c>
       <c r="K354">
-        <v>6346945</v>
+        <v>6346941</v>
       </c>
       <c r="L354" t="s">
         <v>25</v>
@@ -23898,13 +23953,13 @@
         <v>26</v>
       </c>
       <c r="S354">
-        <v>1112262</v>
+        <v>4721220</v>
       </c>
       <c r="T354">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="355" spans="1:20" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="355" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A355" t="s">
         <v>20</v>
       </c>
@@ -23912,10 +23967,10 @@
         <v>8</v>
       </c>
       <c r="C355">
-        <v>39</v>
+        <v>808</v>
       </c>
       <c r="D355" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E355" t="s">
         <v>372</v>
@@ -23924,19 +23979,19 @@
         <v>373</v>
       </c>
       <c r="G355">
-        <v>6346943</v>
+        <v>6359930</v>
       </c>
       <c r="H355" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="I355">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J355">
         <v>4</v>
       </c>
       <c r="K355">
-        <v>6346943</v>
+        <v>6359930</v>
       </c>
       <c r="L355" t="s">
         <v>25</v>
@@ -23960,13 +24015,13 @@
         <v>26</v>
       </c>
       <c r="S355">
-        <v>3013004</v>
+        <v>1156444</v>
       </c>
       <c r="T355">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="356" spans="1:20" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="356" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A356" t="s">
         <v>20</v>
       </c>
@@ -23974,10 +24029,10 @@
         <v>8</v>
       </c>
       <c r="C356">
-        <v>808</v>
+        <v>39</v>
       </c>
       <c r="D356" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E356" t="s">
         <v>372</v>
@@ -23986,10 +24041,10 @@
         <v>373</v>
       </c>
       <c r="G356">
-        <v>6346952</v>
+        <v>6346939</v>
       </c>
       <c r="H356" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="I356">
         <v>2</v>
@@ -23998,7 +24053,7 @@
         <v>4</v>
       </c>
       <c r="K356">
-        <v>6346952</v>
+        <v>6346939</v>
       </c>
       <c r="L356" t="s">
         <v>25</v>
@@ -24028,7 +24083,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="357" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A357" t="s">
         <v>20</v>
       </c>
@@ -24036,10 +24091,10 @@
         <v>8</v>
       </c>
       <c r="C357">
-        <v>39</v>
+        <v>808</v>
       </c>
       <c r="D357" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E357" t="s">
         <v>372</v>
@@ -24048,19 +24103,19 @@
         <v>373</v>
       </c>
       <c r="G357">
-        <v>6346944</v>
+        <v>6346954</v>
       </c>
       <c r="H357" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="I357">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J357">
         <v>4</v>
       </c>
       <c r="K357">
-        <v>6346944</v>
+        <v>6346954</v>
       </c>
       <c r="L357" t="s">
         <v>25</v>
@@ -24084,13 +24139,13 @@
         <v>26</v>
       </c>
       <c r="S357">
-        <v>2923606</v>
+        <v>4721220</v>
       </c>
       <c r="T357">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="358" spans="1:20" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="358" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A358" t="s">
         <v>20</v>
       </c>
@@ -24098,10 +24153,10 @@
         <v>8</v>
       </c>
       <c r="C358">
-        <v>808</v>
+        <v>39</v>
       </c>
       <c r="D358" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E358" t="s">
         <v>372</v>
@@ -24110,19 +24165,19 @@
         <v>373</v>
       </c>
       <c r="G358">
-        <v>6346955</v>
+        <v>6346722</v>
       </c>
       <c r="H358" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="I358">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J358">
         <v>4</v>
       </c>
       <c r="K358">
-        <v>6346955</v>
+        <v>6346722</v>
       </c>
       <c r="L358" t="s">
         <v>25</v>
@@ -24146,13 +24201,13 @@
         <v>26</v>
       </c>
       <c r="S358">
-        <v>1121323</v>
+        <v>2117533</v>
       </c>
       <c r="T358">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="359" spans="1:20" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="359" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A359" t="s">
         <v>20</v>
       </c>
@@ -24160,10 +24215,10 @@
         <v>8</v>
       </c>
       <c r="C359">
-        <v>808</v>
+        <v>39</v>
       </c>
       <c r="D359" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E359" t="s">
         <v>372</v>
@@ -24172,19 +24227,19 @@
         <v>373</v>
       </c>
       <c r="G359">
-        <v>6346956</v>
+        <v>6346940</v>
       </c>
       <c r="H359" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="I359">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J359">
         <v>4</v>
       </c>
       <c r="K359">
-        <v>6346956</v>
+        <v>6346940</v>
       </c>
       <c r="L359" t="s">
         <v>25</v>
@@ -24208,13 +24263,13 @@
         <v>26</v>
       </c>
       <c r="S359">
-        <v>2148154</v>
+        <v>7208507</v>
       </c>
       <c r="T359">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="360" spans="1:20" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="360" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A360" t="s">
         <v>20</v>
       </c>
@@ -24222,10 +24277,10 @@
         <v>8</v>
       </c>
       <c r="C360">
-        <v>808</v>
+        <v>39</v>
       </c>
       <c r="D360" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E360" t="s">
         <v>372</v>
@@ -24234,19 +24289,19 @@
         <v>373</v>
       </c>
       <c r="G360">
-        <v>6346957</v>
+        <v>6346942</v>
       </c>
       <c r="H360" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="I360">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J360">
         <v>4</v>
       </c>
       <c r="K360">
-        <v>6346957</v>
+        <v>6346942</v>
       </c>
       <c r="L360" t="s">
         <v>25</v>
@@ -24270,13 +24325,13 @@
         <v>26</v>
       </c>
       <c r="S360">
-        <v>3013004</v>
+        <v>1121323</v>
       </c>
       <c r="T360">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="361" spans="1:20" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="361" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A361" t="s">
         <v>20</v>
       </c>
@@ -24296,19 +24351,19 @@
         <v>373</v>
       </c>
       <c r="G361">
-        <v>6346958</v>
+        <v>6346760</v>
       </c>
       <c r="H361" t="s">
         <v>77</v>
       </c>
       <c r="I361">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J361">
         <v>4</v>
       </c>
       <c r="K361">
-        <v>6346958</v>
+        <v>6346760</v>
       </c>
       <c r="L361" t="s">
         <v>25</v>
@@ -24332,13 +24387,13 @@
         <v>26</v>
       </c>
       <c r="S361">
-        <v>1112262</v>
+        <v>2117533</v>
       </c>
       <c r="T361">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="362" spans="1:20" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="362" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A362" t="s">
         <v>20</v>
       </c>
@@ -24346,10 +24401,10 @@
         <v>8</v>
       </c>
       <c r="C362">
-        <v>808</v>
+        <v>39</v>
       </c>
       <c r="D362" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E362" t="s">
         <v>372</v>
@@ -24358,19 +24413,19 @@
         <v>373</v>
       </c>
       <c r="G362">
-        <v>6359921</v>
+        <v>6346945</v>
       </c>
       <c r="H362" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="I362">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J362">
         <v>4</v>
       </c>
       <c r="K362">
-        <v>6359921</v>
+        <v>6346945</v>
       </c>
       <c r="L362" t="s">
         <v>25</v>
@@ -24394,13 +24449,13 @@
         <v>26</v>
       </c>
       <c r="S362">
-        <v>2923606</v>
+        <v>1112262</v>
       </c>
       <c r="T362">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="363" spans="1:20" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="363" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A363" t="s">
         <v>20</v>
       </c>
@@ -24462,7 +24517,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="364" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A364" t="s">
         <v>20</v>
       </c>
@@ -24524,7 +24579,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="365" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A365" t="s">
         <v>20</v>
       </c>
@@ -24586,7 +24641,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="366" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A366" t="s">
         <v>20</v>
       </c>
@@ -24648,7 +24703,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="367" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A367" t="s">
         <v>20</v>
       </c>
@@ -24710,7 +24765,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="368" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A368" t="s">
         <v>20</v>
       </c>
@@ -24772,7 +24827,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="369" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A369" t="s">
         <v>20</v>
       </c>
@@ -24834,7 +24889,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="370" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A370" t="s">
         <v>20</v>
       </c>
@@ -24896,7 +24951,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="371" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A371" t="s">
         <v>20</v>
       </c>
@@ -24958,7 +25013,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="372" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A372" t="s">
         <v>20</v>
       </c>
@@ -25020,7 +25075,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="373" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A373" t="s">
         <v>20</v>
       </c>
@@ -25082,7 +25137,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="374" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A374" t="s">
         <v>20</v>
       </c>
@@ -25144,7 +25199,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="375" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A375" t="s">
         <v>20</v>
       </c>
@@ -25206,7 +25261,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="376" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A376" t="s">
         <v>20</v>
       </c>
@@ -25268,7 +25323,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="377" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A377" t="s">
         <v>20</v>
       </c>
@@ -25330,7 +25385,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="378" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A378" t="s">
         <v>20</v>
       </c>
@@ -25392,7 +25447,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="379" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A379" t="s">
         <v>20</v>
       </c>
@@ -25454,7 +25509,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="380" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A380" t="s">
         <v>20</v>
       </c>
@@ -25516,7 +25571,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="381" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A381" t="s">
         <v>20</v>
       </c>
@@ -25578,7 +25633,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="382" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A382" t="s">
         <v>20</v>
       </c>
@@ -25640,7 +25695,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="383" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A383" t="s">
         <v>20</v>
       </c>
@@ -25702,7 +25757,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="384" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A384" t="s">
         <v>20</v>
       </c>
@@ -25764,7 +25819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="385" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A385" t="s">
         <v>20</v>
       </c>
@@ -25826,7 +25881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="386" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A386" t="s">
         <v>20</v>
       </c>
@@ -25840,25 +25895,25 @@
         <v>52</v>
       </c>
       <c r="E386" t="s">
-        <v>401</v>
+        <v>372</v>
       </c>
       <c r="F386" t="s">
-        <v>402</v>
+        <v>373</v>
       </c>
       <c r="G386">
-        <v>6346713</v>
+        <v>6346943</v>
       </c>
       <c r="H386" t="s">
         <v>24</v>
       </c>
       <c r="I386">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J386">
         <v>4</v>
       </c>
       <c r="K386">
-        <v>6346713</v>
+        <v>6346943</v>
       </c>
       <c r="L386" t="s">
         <v>25</v>
@@ -25876,19 +25931,19 @@
         <v>0</v>
       </c>
       <c r="Q386">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R386" t="s">
         <v>26</v>
       </c>
       <c r="S386">
-        <v>1099807</v>
+        <v>3013004</v>
       </c>
       <c r="T386">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="387" spans="1:20" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="387" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A387" t="s">
         <v>20</v>
       </c>
@@ -25896,31 +25951,31 @@
         <v>8</v>
       </c>
       <c r="C387">
-        <v>39</v>
+        <v>808</v>
       </c>
       <c r="D387" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E387" t="s">
-        <v>401</v>
+        <v>372</v>
       </c>
       <c r="F387" t="s">
-        <v>402</v>
+        <v>373</v>
       </c>
       <c r="G387">
-        <v>6346750</v>
+        <v>6346952</v>
       </c>
       <c r="H387" t="s">
         <v>77</v>
       </c>
       <c r="I387">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J387">
         <v>4</v>
       </c>
       <c r="K387">
-        <v>6346750</v>
+        <v>6346952</v>
       </c>
       <c r="L387" t="s">
         <v>25</v>
@@ -25938,19 +25993,19 @@
         <v>0</v>
       </c>
       <c r="Q387">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R387" t="s">
         <v>26</v>
       </c>
       <c r="S387">
-        <v>1099807</v>
+        <v>1540100</v>
       </c>
       <c r="T387">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="388" spans="1:20" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="388" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A388" t="s">
         <v>20</v>
       </c>
@@ -25958,31 +26013,31 @@
         <v>8</v>
       </c>
       <c r="C388">
-        <v>808</v>
+        <v>39</v>
       </c>
       <c r="D388" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E388" t="s">
-        <v>401</v>
+        <v>372</v>
       </c>
       <c r="F388" t="s">
-        <v>402</v>
+        <v>373</v>
       </c>
       <c r="G388">
-        <v>6346750</v>
+        <v>6346944</v>
       </c>
       <c r="H388" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="I388">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J388">
         <v>4</v>
       </c>
       <c r="K388">
-        <v>6346750</v>
+        <v>6346944</v>
       </c>
       <c r="L388" t="s">
         <v>25</v>
@@ -26000,19 +26055,19 @@
         <v>0</v>
       </c>
       <c r="Q388">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R388" t="s">
         <v>26</v>
       </c>
       <c r="S388">
-        <v>1099807</v>
+        <v>2923606</v>
       </c>
       <c r="T388">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="389" spans="1:20" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="389" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A389" t="s">
         <v>20</v>
       </c>
@@ -26074,7 +26129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="390" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A390" t="s">
         <v>20</v>
       </c>
@@ -26136,7 +26191,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="391" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A391" t="s">
         <v>20</v>
       </c>
@@ -26198,7 +26253,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="392" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A392" t="s">
         <v>20</v>
       </c>
@@ -26260,7 +26315,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="393" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A393" t="s">
         <v>20</v>
       </c>
@@ -26322,7 +26377,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="394" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A394" t="s">
         <v>20</v>
       </c>
@@ -26384,7 +26439,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="395" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A395" t="s">
         <v>20</v>
       </c>
@@ -26446,7 +26501,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="396" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A396" t="s">
         <v>20</v>
       </c>
@@ -26508,7 +26563,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="397" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A397" t="s">
         <v>20</v>
       </c>
@@ -26570,7 +26625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="398" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A398" t="s">
         <v>20</v>
       </c>
@@ -26632,7 +26687,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="399" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A399" t="s">
         <v>20</v>
       </c>
@@ -26694,7 +26749,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="400" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A400" t="s">
         <v>20</v>
       </c>
@@ -26756,7 +26811,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="401" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A401" t="s">
         <v>20</v>
       </c>
@@ -26818,7 +26873,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="402" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A402" t="s">
         <v>20</v>
       </c>
@@ -26880,7 +26935,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="403" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A403" t="s">
         <v>20</v>
       </c>
@@ -26942,7 +26997,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="404" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A404" t="s">
         <v>20</v>
       </c>
@@ -27004,7 +27059,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="405" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A405" t="s">
         <v>20</v>
       </c>
@@ -27066,7 +27121,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="406" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A406" t="s">
         <v>20</v>
       </c>
@@ -27128,7 +27183,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="407" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A407" t="s">
         <v>20</v>
       </c>
@@ -27136,37 +27191,37 @@
         <v>8</v>
       </c>
       <c r="C407">
-        <v>39</v>
+        <v>808</v>
       </c>
       <c r="D407" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E407" t="s">
-        <v>419</v>
+        <v>372</v>
       </c>
       <c r="F407" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="G407">
-        <v>6346712</v>
+        <v>6346955</v>
       </c>
       <c r="H407" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="I407">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J407">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K407">
-        <v>6346712</v>
+        <v>6346955</v>
       </c>
       <c r="L407" t="s">
         <v>25</v>
       </c>
       <c r="M407">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N407">
         <v>0</v>
@@ -27175,22 +27230,22 @@
         <v>4</v>
       </c>
       <c r="P407">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q407">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R407" t="s">
         <v>26</v>
       </c>
       <c r="S407">
-        <v>1758752</v>
+        <v>1121323</v>
       </c>
       <c r="T407">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="408" spans="1:20" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="408" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A408" t="s">
         <v>20</v>
       </c>
@@ -27204,31 +27259,31 @@
         <v>54</v>
       </c>
       <c r="E408" t="s">
-        <v>419</v>
+        <v>372</v>
       </c>
       <c r="F408" t="s">
-        <v>420</v>
+        <v>373</v>
       </c>
       <c r="G408">
-        <v>6346749</v>
+        <v>6346956</v>
       </c>
       <c r="H408" t="s">
         <v>77</v>
       </c>
       <c r="I408">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J408">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K408">
-        <v>6346749</v>
+        <v>6346956</v>
       </c>
       <c r="L408" t="s">
         <v>25</v>
       </c>
       <c r="M408">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N408">
         <v>0</v>
@@ -27237,22 +27292,22 @@
         <v>4</v>
       </c>
       <c r="P408">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q408">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R408" t="s">
         <v>26</v>
       </c>
       <c r="S408">
-        <v>1758752</v>
+        <v>2148154</v>
       </c>
       <c r="T408">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="409" spans="1:20" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="409" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A409" t="s">
         <v>20</v>
       </c>
@@ -27314,7 +27369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="410" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A410" t="s">
         <v>20</v>
       </c>
@@ -27376,7 +27431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="411" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A411" t="s">
         <v>20</v>
       </c>
@@ -27390,31 +27445,31 @@
         <v>54</v>
       </c>
       <c r="E411" t="s">
-        <v>423</v>
+        <v>372</v>
       </c>
       <c r="F411" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="G411">
-        <v>6346726</v>
+        <v>6346957</v>
       </c>
       <c r="H411" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="I411">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J411">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K411">
-        <v>6346726</v>
+        <v>6346957</v>
       </c>
       <c r="L411" t="s">
         <v>25</v>
       </c>
       <c r="M411">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N411">
         <v>0</v>
@@ -27423,10 +27478,10 @@
         <v>4</v>
       </c>
       <c r="P411">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q411">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R411" t="s">
         <v>26</v>
@@ -27435,10 +27490,10 @@
         <v>3013004</v>
       </c>
       <c r="T411">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="412" spans="1:20" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="412" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A412" t="s">
         <v>20</v>
       </c>
@@ -27446,37 +27501,37 @@
         <v>8</v>
       </c>
       <c r="C412">
-        <v>39</v>
+        <v>808</v>
       </c>
       <c r="D412" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E412" t="s">
-        <v>423</v>
+        <v>372</v>
       </c>
       <c r="F412" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="G412">
-        <v>6346726</v>
+        <v>6346958</v>
       </c>
       <c r="H412" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="I412">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J412">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K412">
-        <v>6346726</v>
+        <v>6346958</v>
       </c>
       <c r="L412" t="s">
         <v>25</v>
       </c>
       <c r="M412">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N412">
         <v>0</v>
@@ -27485,22 +27540,22 @@
         <v>4</v>
       </c>
       <c r="P412">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q412">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R412" t="s">
         <v>26</v>
       </c>
       <c r="S412">
-        <v>3013004</v>
+        <v>1112262</v>
       </c>
       <c r="T412">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="413" spans="1:20" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="413" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A413" t="s">
         <v>20</v>
       </c>
@@ -27562,7 +27617,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="414" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A414" t="s">
         <v>20</v>
       </c>
@@ -27624,7 +27679,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="415" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A415" t="s">
         <v>20</v>
       </c>
@@ -27686,7 +27741,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="416" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A416" t="s">
         <v>20</v>
       </c>
@@ -27748,7 +27803,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="417" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A417" t="s">
         <v>20</v>
       </c>
@@ -27810,7 +27865,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="418" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A418" t="s">
         <v>20</v>
       </c>
@@ -27872,7 +27927,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="419" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A419" t="s">
         <v>20</v>
       </c>
@@ -27934,7 +27989,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="420" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A420" t="s">
         <v>20</v>
       </c>
@@ -27996,7 +28051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="421" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A421" t="s">
         <v>20</v>
       </c>
@@ -28058,7 +28113,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="422" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A422" t="s">
         <v>20</v>
       </c>
@@ -28120,7 +28175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="423" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A423" t="s">
         <v>20</v>
       </c>
@@ -28182,7 +28237,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="424" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A424" t="s">
         <v>20</v>
       </c>
@@ -28244,7 +28299,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="425" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A425" t="s">
         <v>20</v>
       </c>
@@ -28306,7 +28361,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="426" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A426" t="s">
         <v>20</v>
       </c>
@@ -28368,7 +28423,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="427" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A427" t="s">
         <v>20</v>
       </c>
@@ -28430,7 +28485,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="428" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A428" t="s">
         <v>20</v>
       </c>
@@ -28492,7 +28547,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="429" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A429" t="s">
         <v>20</v>
       </c>
@@ -28554,7 +28609,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="430" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A430" t="s">
         <v>20</v>
       </c>
@@ -28616,7 +28671,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="431" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A431" t="s">
         <v>20</v>
       </c>
@@ -28678,7 +28733,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="432" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A432" t="s">
         <v>20</v>
       </c>
@@ -28740,7 +28795,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="433" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A433" t="s">
         <v>20</v>
       </c>
@@ -28802,7 +28857,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="434" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A434" t="s">
         <v>20</v>
       </c>
@@ -28864,7 +28919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="435" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A435" t="s">
         <v>20</v>
       </c>
@@ -28926,7 +28981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="436" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A436" t="s">
         <v>20</v>
       </c>
@@ -28988,7 +29043,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="437" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A437" t="s">
         <v>20</v>
       </c>
@@ -29050,7 +29105,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="438" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A438" t="s">
         <v>20</v>
       </c>
@@ -29112,7 +29167,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="439" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A439" t="s">
         <v>20</v>
       </c>
@@ -29174,7 +29229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="440" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A440" t="s">
         <v>20</v>
       </c>
@@ -29236,7 +29291,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="441" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A441" t="s">
         <v>20</v>
       </c>
@@ -29298,7 +29353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="442" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A442" t="s">
         <v>20</v>
       </c>
@@ -29360,7 +29415,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="443" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A443" t="s">
         <v>20</v>
       </c>
@@ -29422,7 +29477,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="444" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A444" t="s">
         <v>20</v>
       </c>
@@ -29484,7 +29539,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="445" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A445" t="s">
         <v>20</v>
       </c>
@@ -29546,7 +29601,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="446" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A446" t="s">
         <v>20</v>
       </c>
@@ -29608,7 +29663,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="447" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A447" t="s">
         <v>20</v>
       </c>
@@ -29670,7 +29725,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="448" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A448" t="s">
         <v>20</v>
       </c>
@@ -29732,7 +29787,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="449" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A449" t="s">
         <v>20</v>
       </c>
@@ -29794,7 +29849,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="450" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A450" t="s">
         <v>20</v>
       </c>
@@ -29856,7 +29911,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="451" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A451" t="s">
         <v>20</v>
       </c>
@@ -29918,7 +29973,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="452" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A452" t="s">
         <v>20</v>
       </c>
@@ -29980,7 +30035,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="453" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A453" t="s">
         <v>20</v>
       </c>
@@ -30042,7 +30097,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="454" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A454" t="s">
         <v>20</v>
       </c>
@@ -30104,7 +30159,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="455" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A455" t="s">
         <v>20</v>
       </c>
@@ -30166,7 +30221,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="456" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A456" t="s">
         <v>20</v>
       </c>
@@ -30228,7 +30283,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="457" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A457" t="s">
         <v>20</v>
       </c>
@@ -30290,7 +30345,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="458" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A458" t="s">
         <v>20</v>
       </c>
@@ -30352,7 +30407,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="459" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A459" t="s">
         <v>20</v>
       </c>
@@ -30414,7 +30469,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="460" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A460" t="s">
         <v>20</v>
       </c>
@@ -30476,7 +30531,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="461" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A461" t="s">
         <v>20</v>
       </c>
@@ -30538,7 +30593,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="462" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A462" t="s">
         <v>20</v>
       </c>
@@ -30600,7 +30655,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="463" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A463" t="s">
         <v>20</v>
       </c>
@@ -30662,7 +30717,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="464" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A464" t="s">
         <v>20</v>
       </c>
@@ -30724,7 +30779,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="465" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A465" t="s">
         <v>20</v>
       </c>
@@ -30786,7 +30841,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="466" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A466" t="s">
         <v>20</v>
       </c>
@@ -30848,7 +30903,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="467" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A467" t="s">
         <v>20</v>
       </c>
@@ -30910,7 +30965,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="468" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A468" t="s">
         <v>20</v>
       </c>
@@ -30972,7 +31027,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="469" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A469" t="s">
         <v>20</v>
       </c>
@@ -31034,7 +31089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="470" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A470" t="s">
         <v>20</v>
       </c>
@@ -31096,7 +31151,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="471" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A471" t="s">
         <v>20</v>
       </c>
@@ -31158,7 +31213,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="472" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A472" t="s">
         <v>20</v>
       </c>
@@ -31220,7 +31275,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="473" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A473" t="s">
         <v>20</v>
       </c>
@@ -31282,7 +31337,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="474" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A474" t="s">
         <v>20</v>
       </c>
@@ -31344,7 +31399,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="475" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A475" t="s">
         <v>20</v>
       </c>
@@ -31406,7 +31461,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="476" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A476" t="s">
         <v>20</v>
       </c>
@@ -31468,7 +31523,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="477" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A477" t="s">
         <v>20</v>
       </c>
@@ -31530,7 +31585,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="478" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A478" t="s">
         <v>20</v>
       </c>
@@ -31592,7 +31647,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="479" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A479" t="s">
         <v>20</v>
       </c>
@@ -31654,7 +31709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="480" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A480" t="s">
         <v>20</v>
       </c>
@@ -31716,7 +31771,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="481" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A481" t="s">
         <v>20</v>
       </c>
@@ -31778,7 +31833,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="482" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A482" t="s">
         <v>20</v>
       </c>
@@ -31840,7 +31895,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="483" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A483" t="s">
         <v>20</v>
       </c>
@@ -31902,7 +31957,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="484" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A484" t="s">
         <v>20</v>
       </c>
@@ -31964,7 +32019,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="485" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A485" t="s">
         <v>20</v>
       </c>
@@ -32026,7 +32081,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="486" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A486" t="s">
         <v>20</v>
       </c>
@@ -32088,7 +32143,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="487" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A487" t="s">
         <v>20</v>
       </c>
@@ -32150,7 +32205,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="488" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A488" t="s">
         <v>20</v>
       </c>
@@ -32212,7 +32267,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="489" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A489" t="s">
         <v>20</v>
       </c>
@@ -32274,7 +32329,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="490" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A490" t="s">
         <v>20</v>
       </c>
@@ -32336,7 +32391,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="491" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A491" t="s">
         <v>20</v>
       </c>
@@ -32398,7 +32453,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="492" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A492" t="s">
         <v>20</v>
       </c>
@@ -32460,7 +32515,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="493" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A493" t="s">
         <v>20</v>
       </c>
@@ -32522,7 +32577,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="494" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A494" t="s">
         <v>20</v>
       </c>
@@ -32584,7 +32639,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="495" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A495" t="s">
         <v>20</v>
       </c>
@@ -32646,7 +32701,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="496" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A496" t="s">
         <v>20</v>
       </c>
@@ -32708,7 +32763,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="497" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A497" t="s">
         <v>20</v>
       </c>
@@ -32770,7 +32825,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="498" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A498" t="s">
         <v>20</v>
       </c>
@@ -32832,7 +32887,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="499" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A499" t="s">
         <v>20</v>
       </c>
@@ -32894,7 +32949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="500" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A500" t="s">
         <v>20</v>
       </c>
@@ -32956,7 +33011,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="501" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A501" t="s">
         <v>20</v>
       </c>
@@ -33018,7 +33073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="502" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A502" t="s">
         <v>20</v>
       </c>
@@ -33080,7 +33135,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="503" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A503" t="s">
         <v>20</v>
       </c>
@@ -33142,7 +33197,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="504" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A504" t="s">
         <v>20</v>
       </c>
@@ -33204,7 +33259,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="505" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A505" t="s">
         <v>20</v>
       </c>
@@ -33266,7 +33321,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="506" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A506" t="s">
         <v>20</v>
       </c>
@@ -33328,7 +33383,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="507" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A507" t="s">
         <v>20</v>
       </c>
@@ -33390,7 +33445,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="508" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A508" t="s">
         <v>20</v>
       </c>
@@ -33452,7 +33507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="509" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A509" t="s">
         <v>20</v>
       </c>
@@ -33514,7 +33569,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="510" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A510" t="s">
         <v>20</v>
       </c>
@@ -33576,7 +33631,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="511" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A511" t="s">
         <v>20</v>
       </c>
@@ -33638,7 +33693,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="512" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A512" t="s">
         <v>20</v>
       </c>
@@ -33700,7 +33755,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="513" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A513" t="s">
         <v>20</v>
       </c>
@@ -33762,7 +33817,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="514" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A514" t="s">
         <v>20</v>
       </c>
@@ -33824,7 +33879,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="515" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A515" t="s">
         <v>20</v>
       </c>
@@ -33886,7 +33941,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="516" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A516" t="s">
         <v>20</v>
       </c>
@@ -33948,7 +34003,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="517" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A517" t="s">
         <v>20</v>
       </c>
@@ -34010,7 +34065,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="518" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A518" t="s">
         <v>20</v>
       </c>
@@ -34072,7 +34127,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="519" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A519" t="s">
         <v>20</v>
       </c>
@@ -34134,7 +34189,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="520" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A520" t="s">
         <v>20</v>
       </c>
@@ -34196,7 +34251,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="521" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A521" t="s">
         <v>20</v>
       </c>
@@ -34258,7 +34313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="522" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A522" t="s">
         <v>20</v>
       </c>
@@ -34320,7 +34375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="523" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A523" t="s">
         <v>20</v>
       </c>
@@ -34382,7 +34437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="524" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A524" t="s">
         <v>20</v>
       </c>
@@ -34444,7 +34499,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="525" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A525" t="s">
         <v>20</v>
       </c>
@@ -34506,7 +34561,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="526" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A526" t="s">
         <v>20</v>
       </c>
@@ -34568,7 +34623,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="527" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A527" t="s">
         <v>20</v>
       </c>
@@ -34630,7 +34685,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="528" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A528" t="s">
         <v>20</v>
       </c>
@@ -34692,7 +34747,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="529" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A529" t="s">
         <v>20</v>
       </c>
@@ -34754,7 +34809,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="530" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A530" t="s">
         <v>20</v>
       </c>
@@ -34816,7 +34871,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="531" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A531" t="s">
         <v>20</v>
       </c>
@@ -34878,7 +34933,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="532" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A532" t="s">
         <v>20</v>
       </c>
@@ -34886,37 +34941,37 @@
         <v>8</v>
       </c>
       <c r="C532">
-        <v>39</v>
+        <v>808</v>
       </c>
       <c r="D532" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E532" t="s">
-        <v>533</v>
+        <v>372</v>
       </c>
       <c r="F532" t="s">
-        <v>532</v>
+        <v>373</v>
       </c>
       <c r="G532">
-        <v>6346720</v>
+        <v>6359921</v>
       </c>
       <c r="H532" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="I532">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J532">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K532">
-        <v>6346720</v>
+        <v>6359921</v>
       </c>
       <c r="L532" t="s">
         <v>25</v>
       </c>
       <c r="M532">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N532">
         <v>0</v>
@@ -34925,60 +34980,60 @@
         <v>4</v>
       </c>
       <c r="P532">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q532">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R532" t="s">
         <v>26</v>
       </c>
       <c r="S532">
-        <v>3473810</v>
+        <v>2923606</v>
       </c>
       <c r="T532">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="533" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A533" t="s">
+        <v>20</v>
+      </c>
+      <c r="B533">
+        <v>8</v>
+      </c>
+      <c r="C533">
         <v>39</v>
       </c>
-    </row>
-    <row r="533" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A533" t="s">
-        <v>20</v>
-      </c>
-      <c r="B533">
-        <v>8</v>
-      </c>
-      <c r="C533">
-        <v>808</v>
-      </c>
       <c r="D533" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E533" t="s">
-        <v>533</v>
+        <v>370</v>
       </c>
       <c r="F533" t="s">
-        <v>532</v>
+        <v>371</v>
       </c>
       <c r="G533">
-        <v>6346758</v>
+        <v>6351265</v>
       </c>
       <c r="H533" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="I533">
         <v>1</v>
       </c>
       <c r="J533">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K533">
-        <v>6346758</v>
+        <v>6351265</v>
       </c>
       <c r="L533" t="s">
         <v>25</v>
       </c>
       <c r="M533">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N533">
         <v>0</v>
@@ -34987,22 +35042,22 @@
         <v>4</v>
       </c>
       <c r="P533">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q533">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R533" t="s">
         <v>26</v>
       </c>
       <c r="S533">
-        <v>3473810</v>
+        <v>7208507</v>
       </c>
       <c r="T533">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="534" spans="1:20" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="534" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A534" t="s">
         <v>20</v>
       </c>
@@ -35066,5 +35121,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>